--- a/templates/billing.xlsx
+++ b/templates/billing.xlsx
@@ -1,25 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s\Documents\JeseanRentals\Data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="8055"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300"/>
   </bookViews>
   <sheets>
-    <sheet name="april may" sheetId="1" r:id="rId1"/>
+    <sheet name="APRIL-MAY 2026" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
@@ -38,7 +28,7 @@
     <t>UPS BILLING STATEMENT</t>
   </si>
   <si>
-    <t>CUSTOMER: BUHANGIN E/S                                                                                                               DATE:6/1/2026</t>
+    <t>CUSTOMER: PINAMANCULAN NHS                                                                                              DATE:6/1/2026</t>
   </si>
   <si>
     <t xml:space="preserve">UNIT </t>
@@ -50,7 +40,7 @@
     <t>Price</t>
   </si>
   <si>
-    <t>1 EPSON L120 and 1 EPSON 3n1</t>
+    <t>1 EPSON L3210</t>
   </si>
   <si>
     <t xml:space="preserve">UNLIMITED PRINTING SERVICES </t>
@@ -81,7 +71,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="12">
+  <fonts count="13">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -247,62 +244,62 @@
   </cellStyleXfs>
   <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -332,14 +329,16 @@
     <xdr:ext cx="1381125" cy="923925"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="image1.png" title="Image">
+        <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F1113271-2B77-4E07-81E7-8C3D9092C5EE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
@@ -349,16 +348,15 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2962275" y="142875"/>
-          <a:ext cx="1381125" cy="923925"/>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:noFill/>
       </xdr:spPr>
     </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
+    <xdr:clientData/>
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
@@ -370,14 +368,16 @@
     <xdr:ext cx="1381125" cy="923925"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="image1.png" title="Image">
+        <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{88AA5431-3F2E-4F28-BA18-6FB0DB854E34}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
@@ -387,17 +387,102 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2962275" y="6096000"/>
-          <a:ext cx="1381125" cy="923925"/>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:noFill/>
       </xdr:spPr>
     </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
+    <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>66674</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>171451</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>21433</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect l="29119" t="14773" r="35653" b="39488"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="647699" y="8905876"/>
+          <a:ext cx="1771651" cy="3450432"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>57149</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>411958</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect l="29119" t="14773" r="35653" b="39488"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="638174" y="3009900"/>
+          <a:ext cx="1771651" cy="3421858"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -668,574 +753,575 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N708"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="26.140625" style="2" customWidth="1"/>
-    <col min="3" max="4" width="8.7109375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="6.85546875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="10" style="2" customWidth="1"/>
-    <col min="7" max="7" width="8.7109375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="16.140625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="8.7109375" style="2" customWidth="1"/>
-    <col min="10" max="10" width="12.28515625" style="2" customWidth="1"/>
-    <col min="11" max="14" width="8.7109375" style="2" customWidth="1"/>
-    <col min="15" max="16384" width="14.42578125" style="2"/>
+    <col min="1" max="1" width="8.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="26.140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="8.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.85546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="10" style="1" customWidth="1"/>
+    <col min="7" max="7" width="8.7109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="16.140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="8.7109375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12.28515625" style="1" customWidth="1"/>
+    <col min="11" max="14" width="8.7109375" style="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" customWidth="1"/>
+    <col min="16" max="16384" width="14.42578125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="38.25" customHeight="1">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
     </row>
     <row r="2" spans="1:14" ht="38.25" customHeight="1">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
     </row>
     <row r="3" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
     </row>
     <row r="4" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
     </row>
     <row r="5" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="7"/>
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="4"/>
     </row>
     <row r="6" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10"/>
     </row>
     <row r="7" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="N7" s="10"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+      <c r="N7" s="5"/>
     </row>
     <row r="8" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="12"/>
-      <c r="C8" s="11" t="s">
+      <c r="B8" s="15"/>
+      <c r="C8" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="11" t="s">
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="J8" s="12"/>
+      <c r="J8" s="15"/>
     </row>
     <row r="9" spans="1:14" ht="21" customHeight="1">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="12"/>
-      <c r="C9" s="15" t="s">
+      <c r="B9" s="15"/>
+      <c r="C9" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="16"/>
-      <c r="J9" s="12"/>
-      <c r="M9" s="17"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="15"/>
+      <c r="M9" s="6"/>
     </row>
     <row r="10" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A10" s="14"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="15" t="s">
+      <c r="A10" s="17"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="16">
-        <v>2800</v>
-      </c>
-      <c r="J10" s="12"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="19">
+        <v>1500</v>
+      </c>
+      <c r="J10" s="15"/>
     </row>
     <row r="11" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A11" s="14"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="15" t="s">
+      <c r="A11" s="17"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="16">
-        <v>2800</v>
-      </c>
-      <c r="J11" s="12"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="15"/>
+      <c r="I11" s="19">
+        <v>1500</v>
+      </c>
+      <c r="J11" s="15"/>
     </row>
     <row r="12" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A12" s="14"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="12"/>
+      <c r="A12" s="17"/>
+      <c r="B12" s="15"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="15"/>
     </row>
     <row r="13" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A13" s="14"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="16"/>
-      <c r="J13" s="12"/>
+      <c r="A13" s="17"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="15"/>
     </row>
     <row r="14" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A14" s="14"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="16"/>
-      <c r="J14" s="12"/>
+      <c r="A14" s="17"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="15"/>
     </row>
     <row r="15" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A15" s="14"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="16"/>
-      <c r="J15" s="12"/>
+      <c r="A15" s="17"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="15"/>
     </row>
     <row r="16" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A16" s="15"/>
-      <c r="B16" s="12"/>
-      <c r="C16" s="11" t="s">
+      <c r="A16" s="18"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="18">
-        <f>SUM(I9:J15)</f>
-        <v>5600</v>
-      </c>
-      <c r="J16" s="12"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="20">
+        <f>SUM(J10:J11)</f>
+        <v>3000</v>
+      </c>
+      <c r="J16" s="15"/>
     </row>
     <row r="17" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A17" s="17"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="10"/>
+      <c r="J17" s="10"/>
     </row>
     <row r="18" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A18" s="19" t="s">
+      <c r="A18" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="20" t="s">
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="G18" s="21"/>
-      <c r="H18" s="22"/>
-      <c r="I18" s="22"/>
-      <c r="J18" s="22"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="23"/>
+      <c r="I18" s="23"/>
+      <c r="J18" s="23"/>
     </row>
     <row r="19" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A19" s="23" t="s">
+      <c r="A19" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="24" t="s">
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="H19" s="25"/>
-      <c r="I19" s="25"/>
-      <c r="J19" s="25"/>
+      <c r="H19" s="26"/>
+      <c r="I19" s="26"/>
+      <c r="J19" s="26"/>
     </row>
     <row r="20" spans="1:14" ht="76.5" customHeight="1">
-      <c r="A20" s="26"/>
-      <c r="B20" s="26"/>
-      <c r="C20" s="26"/>
-      <c r="D20" s="26"/>
-      <c r="E20" s="26"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="26"/>
-      <c r="H20" s="26"/>
-      <c r="I20" s="26"/>
-      <c r="J20" s="26"/>
-      <c r="N20" s="17"/>
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
+      <c r="N20" s="6"/>
     </row>
     <row r="21" spans="1:14" ht="72" customHeight="1"/>
     <row r="22" spans="1:14" ht="78" customHeight="1">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
-      <c r="J22" s="4"/>
+      <c r="B22" s="10"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="10"/>
+      <c r="I22" s="10"/>
+      <c r="J22" s="10"/>
     </row>
     <row r="23" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="4"/>
+      <c r="B23" s="10"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="10"/>
+      <c r="I23" s="10"/>
+      <c r="J23" s="10"/>
     </row>
     <row r="24" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
-      <c r="I24" s="4"/>
-      <c r="J24" s="4"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="10"/>
+      <c r="I24" s="10"/>
+      <c r="J24" s="10"/>
     </row>
     <row r="25" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A25" s="6"/>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="6"/>
-      <c r="J25" s="7"/>
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
+      <c r="J25" s="4"/>
     </row>
     <row r="26" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
-      <c r="I26" s="4"/>
-      <c r="J26" s="4"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="10"/>
+      <c r="G26" s="10"/>
+      <c r="H26" s="10"/>
+      <c r="I26" s="10"/>
+      <c r="J26" s="10"/>
     </row>
     <row r="27" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A27" s="9" t="s">
+      <c r="A27" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="4"/>
-      <c r="J27" s="4"/>
+      <c r="B27" s="10"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="10"/>
+      <c r="F27" s="10"/>
+      <c r="G27" s="10"/>
+      <c r="H27" s="10"/>
+      <c r="I27" s="10"/>
+      <c r="J27" s="10"/>
     </row>
     <row r="28" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A28" s="11" t="s">
+      <c r="A28" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B28" s="12"/>
-      <c r="C28" s="11" t="s">
+      <c r="B28" s="15"/>
+      <c r="C28" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="12"/>
-      <c r="I28" s="11" t="s">
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="15"/>
+      <c r="I28" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="J28" s="12"/>
+      <c r="J28" s="15"/>
     </row>
     <row r="29" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A29" s="14" t="s">
+      <c r="A29" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="B29" s="12"/>
-      <c r="C29" s="15" t="s">
+      <c r="B29" s="15"/>
+      <c r="C29" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="16"/>
-      <c r="J29" s="12"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="16"/>
+      <c r="H29" s="15"/>
+      <c r="I29" s="19"/>
+      <c r="J29" s="15"/>
     </row>
     <row r="30" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A30" s="14"/>
-      <c r="B30" s="12"/>
-      <c r="C30" s="15" t="s">
+      <c r="A30" s="17"/>
+      <c r="B30" s="15"/>
+      <c r="C30" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="16">
-        <v>2800</v>
-      </c>
-      <c r="J30" s="12"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="16"/>
+      <c r="H30" s="15"/>
+      <c r="I30" s="19">
+        <v>1500</v>
+      </c>
+      <c r="J30" s="15"/>
     </row>
     <row r="31" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A31" s="14"/>
-      <c r="B31" s="12"/>
-      <c r="C31" s="15" t="s">
+      <c r="A31" s="17"/>
+      <c r="B31" s="15"/>
+      <c r="C31" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
-      <c r="G31" s="13"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="16">
-        <v>2800</v>
-      </c>
-      <c r="J31" s="12"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="16"/>
+      <c r="H31" s="15"/>
+      <c r="I31" s="19">
+        <v>1500</v>
+      </c>
+      <c r="J31" s="15"/>
     </row>
     <row r="32" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A32" s="14"/>
-      <c r="B32" s="12"/>
-      <c r="C32" s="15"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="12"/>
-      <c r="I32" s="16"/>
-      <c r="J32" s="12"/>
+      <c r="A32" s="17"/>
+      <c r="B32" s="15"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="16"/>
+      <c r="G32" s="16"/>
+      <c r="H32" s="15"/>
+      <c r="I32" s="19"/>
+      <c r="J32" s="15"/>
     </row>
     <row r="33" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A33" s="14"/>
-      <c r="B33" s="12"/>
-      <c r="C33" s="15"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="13"/>
-      <c r="H33" s="12"/>
-      <c r="I33" s="16"/>
-      <c r="J33" s="12"/>
+      <c r="A33" s="17"/>
+      <c r="B33" s="15"/>
+      <c r="C33" s="18"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="16"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="16"/>
+      <c r="H33" s="15"/>
+      <c r="I33" s="19"/>
+      <c r="J33" s="15"/>
     </row>
     <row r="34" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A34" s="14"/>
-      <c r="B34" s="12"/>
-      <c r="C34" s="15"/>
-      <c r="D34" s="13"/>
-      <c r="E34" s="13"/>
-      <c r="F34" s="13"/>
-      <c r="G34" s="13"/>
-      <c r="H34" s="12"/>
-      <c r="I34" s="16"/>
-      <c r="J34" s="12"/>
+      <c r="A34" s="17"/>
+      <c r="B34" s="15"/>
+      <c r="C34" s="18"/>
+      <c r="D34" s="16"/>
+      <c r="E34" s="16"/>
+      <c r="F34" s="16"/>
+      <c r="G34" s="16"/>
+      <c r="H34" s="15"/>
+      <c r="I34" s="19"/>
+      <c r="J34" s="15"/>
     </row>
     <row r="35" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A35" s="14"/>
-      <c r="B35" s="12"/>
-      <c r="C35" s="15"/>
-      <c r="D35" s="13"/>
-      <c r="E35" s="13"/>
-      <c r="F35" s="13"/>
-      <c r="G35" s="13"/>
-      <c r="H35" s="12"/>
-      <c r="I35" s="16"/>
-      <c r="J35" s="12"/>
+      <c r="A35" s="17"/>
+      <c r="B35" s="15"/>
+      <c r="C35" s="18"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="16"/>
+      <c r="H35" s="15"/>
+      <c r="I35" s="19"/>
+      <c r="J35" s="15"/>
     </row>
     <row r="36" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A36" s="15"/>
-      <c r="B36" s="12"/>
-      <c r="C36" s="11" t="s">
+      <c r="A36" s="18"/>
+      <c r="B36" s="15"/>
+      <c r="C36" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="D36" s="13"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="13"/>
-      <c r="G36" s="13"/>
-      <c r="H36" s="12"/>
-      <c r="I36" s="18">
-        <f>SUM(I29:J35)</f>
-        <v>5600</v>
-      </c>
-      <c r="J36" s="12"/>
+      <c r="D36" s="16"/>
+      <c r="E36" s="16"/>
+      <c r="F36" s="16"/>
+      <c r="G36" s="16"/>
+      <c r="H36" s="15"/>
+      <c r="I36" s="20">
+        <f>SUM(J30:J31)</f>
+        <v>3000</v>
+      </c>
+      <c r="J36" s="15"/>
     </row>
     <row r="37" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A37" s="17"/>
-      <c r="B37" s="17"/>
-      <c r="C37" s="17"/>
-      <c r="D37" s="17"/>
-      <c r="E37" s="5"/>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
-      <c r="I37" s="4"/>
-      <c r="J37" s="4"/>
+      <c r="A37" s="6"/>
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="11"/>
+      <c r="F37" s="10"/>
+      <c r="G37" s="10"/>
+      <c r="H37" s="10"/>
+      <c r="I37" s="10"/>
+      <c r="J37" s="10"/>
     </row>
     <row r="38" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A38" s="19" t="s">
+      <c r="A38" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="17"/>
-      <c r="F38" s="20" t="s">
+      <c r="B38" s="10"/>
+      <c r="C38" s="10"/>
+      <c r="D38" s="10"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="G38" s="21"/>
-      <c r="H38" s="22"/>
-      <c r="I38" s="22"/>
-      <c r="J38" s="22"/>
+      <c r="G38" s="22"/>
+      <c r="H38" s="23"/>
+      <c r="I38" s="23"/>
+      <c r="J38" s="23"/>
     </row>
     <row r="39" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A39" s="23" t="s">
+      <c r="A39" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
-      <c r="E39" s="17"/>
-      <c r="F39" s="17"/>
-      <c r="G39" s="24" t="s">
+      <c r="B39" s="10"/>
+      <c r="C39" s="10"/>
+      <c r="D39" s="10"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="H39" s="25"/>
-      <c r="I39" s="25"/>
-      <c r="J39" s="25"/>
+      <c r="H39" s="26"/>
+      <c r="I39" s="26"/>
+      <c r="J39" s="26"/>
     </row>
     <row r="40" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A40" s="26"/>
-      <c r="B40" s="26"/>
-      <c r="C40" s="26"/>
-      <c r="D40" s="26"/>
-      <c r="E40" s="26"/>
-      <c r="F40" s="26"/>
-      <c r="G40" s="26"/>
-      <c r="H40" s="26"/>
-      <c r="I40" s="26"/>
-      <c r="J40" s="26"/>
+      <c r="A40" s="8"/>
+      <c r="B40" s="8"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="8"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="8"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="8"/>
+      <c r="I40" s="8"/>
+      <c r="J40" s="8"/>
     </row>
     <row r="41" spans="1:10" ht="15.75" customHeight="1"/>
     <row r="42" spans="1:10" ht="15.75" customHeight="1"/>
@@ -1936,55 +2022,55 @@
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:H30"/>
     <mergeCell ref="I30:J30"/>
-    <mergeCell ref="A23:J23"/>
-    <mergeCell ref="A24:J24"/>
     <mergeCell ref="A26:J26"/>
     <mergeCell ref="A27:J27"/>
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="C28:H28"/>
     <mergeCell ref="I28:J28"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="G19:J19"/>
+    <mergeCell ref="A22:J22"/>
+    <mergeCell ref="A23:J23"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:H16"/>
+    <mergeCell ref="I16:J16"/>
     <mergeCell ref="E17:J17"/>
     <mergeCell ref="A18:D18"/>
     <mergeCell ref="G18:J18"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="G19:J19"/>
-    <mergeCell ref="A22:J22"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="C14:H14"/>
+    <mergeCell ref="I14:J14"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="C15:H15"/>
     <mergeCell ref="I15:J15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C16:H16"/>
-    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C12:H12"/>
+    <mergeCell ref="I12:J12"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="C13:H13"/>
     <mergeCell ref="I13:J13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="C14:H14"/>
-    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C10:H10"/>
+    <mergeCell ref="I10:J10"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="C11:H11"/>
     <mergeCell ref="I11:J11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C12:H12"/>
-    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:H8"/>
+    <mergeCell ref="I8:J8"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="C9:H9"/>
     <mergeCell ref="I9:J9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C10:H10"/>
-    <mergeCell ref="I10:J10"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A3:J3"/>
     <mergeCell ref="A4:J4"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="A7:J7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:H8"/>
-    <mergeCell ref="I8:J8"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="77" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
+  <pageSetup paperSize="9" scale="77" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/templates/billing.xlsx
+++ b/templates/billing.xlsx
@@ -400,15 +400,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>66674</xdr:colOff>
+      <xdr:colOff>419100</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>171451</xdr:rowOff>
+      <xdr:rowOff>114301</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>21433</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1465706</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -418,7 +418,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -430,8 +430,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="647699" y="8905876"/>
-          <a:ext cx="1771651" cy="3450432"/>
+          <a:off x="1000125" y="8848726"/>
+          <a:ext cx="1046606" cy="2038349"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -443,25 +443,25 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>57149</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:colOff>504826</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>47626</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>85725</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>411958</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1457326</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>454896</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4"/>
+        <xdr:cNvPr id="6" name="Picture 5"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -473,8 +473,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="638174" y="3009900"/>
-          <a:ext cx="1771651" cy="3421858"/>
+          <a:off x="1085851" y="2733676"/>
+          <a:ext cx="952500" cy="1855070"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1992,6 +1992,7 @@
     <row r="707" ht="15.75" customHeight="1"/>
     <row r="708" ht="15.75" customHeight="1"/>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="74">
     <mergeCell ref="E37:J37"/>
     <mergeCell ref="A38:D38"/>

--- a/templates/billing.xlsx
+++ b/templates/billing.xlsx
@@ -7,7 +7,7 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300"/>
   </bookViews>
   <sheets>
-    <sheet name="APRIL-MAY 2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Billing" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -256,36 +256,10 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -300,6 +274,32 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -782,7 +782,7 @@
       <c r="J1" s="2"/>
     </row>
     <row r="2" spans="1:14" ht="38.25" customHeight="1">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="26" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="10"/>
@@ -796,7 +796,7 @@
       <c r="J2" s="10"/>
     </row>
     <row r="3" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="9" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="10"/>
@@ -810,7 +810,7 @@
       <c r="J3" s="10"/>
     </row>
     <row r="4" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="9" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="10"/>
@@ -836,7 +836,7 @@
       <c r="J5" s="4"/>
     </row>
     <row r="6" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="24" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="10"/>
@@ -850,7 +850,7 @@
       <c r="J6" s="10"/>
     </row>
     <row r="7" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="25" t="s">
         <v>4</v>
       </c>
       <c r="B7" s="10"/>
@@ -865,143 +865,143 @@
       <c r="N7" s="5"/>
     </row>
     <row r="8" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="15"/>
-      <c r="C8" s="14" t="s">
+      <c r="B8" s="18"/>
+      <c r="C8" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="14" t="s">
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="J8" s="15"/>
+      <c r="J8" s="18"/>
     </row>
     <row r="9" spans="1:14" ht="21" customHeight="1">
       <c r="A9" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="15"/>
-      <c r="C9" s="18" t="s">
+      <c r="B9" s="18"/>
+      <c r="C9" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="19"/>
-      <c r="J9" s="15"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="21"/>
+      <c r="J9" s="18"/>
       <c r="M9" s="6"/>
     </row>
     <row r="10" spans="1:14" ht="14.25" customHeight="1">
       <c r="A10" s="17"/>
-      <c r="B10" s="15"/>
-      <c r="C10" s="18" t="s">
+      <c r="B10" s="18"/>
+      <c r="C10" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="19">
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="21">
         <v>1500</v>
       </c>
-      <c r="J10" s="15"/>
+      <c r="J10" s="18"/>
     </row>
     <row r="11" spans="1:14" ht="14.25" customHeight="1">
       <c r="A11" s="17"/>
-      <c r="B11" s="15"/>
-      <c r="C11" s="18" t="s">
+      <c r="B11" s="18"/>
+      <c r="C11" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="19">
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="21">
         <v>1500</v>
       </c>
-      <c r="J11" s="15"/>
+      <c r="J11" s="18"/>
     </row>
     <row r="12" spans="1:14" ht="14.25" customHeight="1">
       <c r="A12" s="17"/>
-      <c r="B12" s="15"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="15"/>
-      <c r="I12" s="19"/>
-      <c r="J12" s="15"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="18"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="18"/>
     </row>
     <row r="13" spans="1:14" ht="14.25" customHeight="1">
       <c r="A13" s="17"/>
-      <c r="B13" s="15"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="15"/>
-      <c r="I13" s="19"/>
-      <c r="J13" s="15"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="21"/>
+      <c r="J13" s="18"/>
     </row>
     <row r="14" spans="1:14" ht="14.25" customHeight="1">
       <c r="A14" s="17"/>
-      <c r="B14" s="15"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="15"/>
-      <c r="I14" s="19"/>
-      <c r="J14" s="15"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="18"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="18"/>
     </row>
     <row r="15" spans="1:14" ht="14.25" customHeight="1">
       <c r="A15" s="17"/>
-      <c r="B15" s="15"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="19"/>
-      <c r="J15" s="15"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="21"/>
+      <c r="J15" s="18"/>
     </row>
     <row r="16" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A16" s="18"/>
-      <c r="B16" s="15"/>
-      <c r="C16" s="14" t="s">
+      <c r="A16" s="19"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="20">
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="18"/>
+      <c r="I16" s="23">
         <f>SUM(J10:J11)</f>
         <v>3000</v>
       </c>
-      <c r="J16" s="15"/>
+      <c r="J16" s="18"/>
     </row>
     <row r="17" spans="1:14" ht="14.25" customHeight="1">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
-      <c r="E17" s="11"/>
+      <c r="E17" s="9"/>
       <c r="F17" s="10"/>
       <c r="G17" s="10"/>
       <c r="H17" s="10"/>
@@ -1009,7 +1009,7 @@
       <c r="J17" s="10"/>
     </row>
     <row r="18" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A18" s="21" t="s">
+      <c r="A18" s="11" t="s">
         <v>13</v>
       </c>
       <c r="B18" s="10"/>
@@ -1019,13 +1019,13 @@
       <c r="F18" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="G18" s="22"/>
-      <c r="H18" s="23"/>
-      <c r="I18" s="23"/>
-      <c r="J18" s="23"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="13"/>
+      <c r="J18" s="13"/>
     </row>
     <row r="19" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A19" s="24" t="s">
+      <c r="A19" s="14" t="s">
         <v>15</v>
       </c>
       <c r="B19" s="10"/>
@@ -1033,12 +1033,12 @@
       <c r="D19" s="10"/>
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
-      <c r="G19" s="25" t="s">
+      <c r="G19" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="H19" s="26"/>
-      <c r="I19" s="26"/>
-      <c r="J19" s="26"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="16"/>
+      <c r="J19" s="16"/>
     </row>
     <row r="20" spans="1:14" ht="76.5" customHeight="1">
       <c r="A20" s="8"/>
@@ -1055,7 +1055,7 @@
     </row>
     <row r="21" spans="1:14" ht="72" customHeight="1"/>
     <row r="22" spans="1:14" ht="78" customHeight="1">
-      <c r="A22" s="9" t="s">
+      <c r="A22" s="26" t="s">
         <v>0</v>
       </c>
       <c r="B22" s="10"/>
@@ -1069,7 +1069,7 @@
       <c r="J22" s="10"/>
     </row>
     <row r="23" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A23" s="11" t="s">
+      <c r="A23" s="9" t="s">
         <v>1</v>
       </c>
       <c r="B23" s="10"/>
@@ -1083,7 +1083,7 @@
       <c r="J23" s="10"/>
     </row>
     <row r="24" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A24" s="11" t="s">
+      <c r="A24" s="9" t="s">
         <v>2</v>
       </c>
       <c r="B24" s="10"/>
@@ -1109,7 +1109,7 @@
       <c r="J25" s="4"/>
     </row>
     <row r="26" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A26" s="12" t="s">
+      <c r="A26" s="24" t="s">
         <v>3</v>
       </c>
       <c r="B26" s="10"/>
@@ -1123,7 +1123,7 @@
       <c r="J26" s="10"/>
     </row>
     <row r="27" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A27" s="13" t="s">
+      <c r="A27" s="25" t="s">
         <v>4</v>
       </c>
       <c r="B27" s="10"/>
@@ -1137,142 +1137,142 @@
       <c r="J27" s="10"/>
     </row>
     <row r="28" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A28" s="14" t="s">
+      <c r="A28" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="B28" s="15"/>
-      <c r="C28" s="14" t="s">
+      <c r="B28" s="18"/>
+      <c r="C28" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="16"/>
-      <c r="H28" s="15"/>
-      <c r="I28" s="14" t="s">
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
+      <c r="H28" s="18"/>
+      <c r="I28" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="J28" s="15"/>
+      <c r="J28" s="18"/>
     </row>
     <row r="29" spans="1:14" ht="15.75" customHeight="1">
       <c r="A29" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="B29" s="15"/>
-      <c r="C29" s="18" t="s">
+      <c r="B29" s="18"/>
+      <c r="C29" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="16"/>
-      <c r="G29" s="16"/>
-      <c r="H29" s="15"/>
-      <c r="I29" s="19"/>
-      <c r="J29" s="15"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="18"/>
+      <c r="I29" s="21"/>
+      <c r="J29" s="18"/>
     </row>
     <row r="30" spans="1:14" ht="15.75" customHeight="1">
       <c r="A30" s="17"/>
-      <c r="B30" s="15"/>
-      <c r="C30" s="18" t="s">
+      <c r="B30" s="18"/>
+      <c r="C30" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="16"/>
-      <c r="G30" s="16"/>
-      <c r="H30" s="15"/>
-      <c r="I30" s="19">
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
+      <c r="H30" s="18"/>
+      <c r="I30" s="21">
         <v>1500</v>
       </c>
-      <c r="J30" s="15"/>
+      <c r="J30" s="18"/>
     </row>
     <row r="31" spans="1:14" ht="15.75" customHeight="1">
       <c r="A31" s="17"/>
-      <c r="B31" s="15"/>
-      <c r="C31" s="18" t="s">
+      <c r="B31" s="18"/>
+      <c r="C31" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="D31" s="16"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="16"/>
-      <c r="H31" s="15"/>
-      <c r="I31" s="19">
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="20"/>
+      <c r="H31" s="18"/>
+      <c r="I31" s="21">
         <v>1500</v>
       </c>
-      <c r="J31" s="15"/>
+      <c r="J31" s="18"/>
     </row>
     <row r="32" spans="1:14" ht="15.75" customHeight="1">
       <c r="A32" s="17"/>
-      <c r="B32" s="15"/>
-      <c r="C32" s="18"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16"/>
-      <c r="F32" s="16"/>
-      <c r="G32" s="16"/>
-      <c r="H32" s="15"/>
-      <c r="I32" s="19"/>
-      <c r="J32" s="15"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="20"/>
+      <c r="H32" s="18"/>
+      <c r="I32" s="21"/>
+      <c r="J32" s="18"/>
     </row>
     <row r="33" spans="1:10" ht="15.75" customHeight="1">
       <c r="A33" s="17"/>
-      <c r="B33" s="15"/>
-      <c r="C33" s="18"/>
-      <c r="D33" s="16"/>
-      <c r="E33" s="16"/>
-      <c r="F33" s="16"/>
-      <c r="G33" s="16"/>
-      <c r="H33" s="15"/>
-      <c r="I33" s="19"/>
-      <c r="J33" s="15"/>
+      <c r="B33" s="18"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="20"/>
+      <c r="H33" s="18"/>
+      <c r="I33" s="21"/>
+      <c r="J33" s="18"/>
     </row>
     <row r="34" spans="1:10" ht="15.75" customHeight="1">
       <c r="A34" s="17"/>
-      <c r="B34" s="15"/>
-      <c r="C34" s="18"/>
-      <c r="D34" s="16"/>
-      <c r="E34" s="16"/>
-      <c r="F34" s="16"/>
-      <c r="G34" s="16"/>
-      <c r="H34" s="15"/>
-      <c r="I34" s="19"/>
-      <c r="J34" s="15"/>
+      <c r="B34" s="18"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="20"/>
+      <c r="H34" s="18"/>
+      <c r="I34" s="21"/>
+      <c r="J34" s="18"/>
     </row>
     <row r="35" spans="1:10" ht="15.75" customHeight="1">
       <c r="A35" s="17"/>
-      <c r="B35" s="15"/>
-      <c r="C35" s="18"/>
-      <c r="D35" s="16"/>
-      <c r="E35" s="16"/>
-      <c r="F35" s="16"/>
-      <c r="G35" s="16"/>
-      <c r="H35" s="15"/>
-      <c r="I35" s="19"/>
-      <c r="J35" s="15"/>
+      <c r="B35" s="18"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="20"/>
+      <c r="G35" s="20"/>
+      <c r="H35" s="18"/>
+      <c r="I35" s="21"/>
+      <c r="J35" s="18"/>
     </row>
     <row r="36" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A36" s="18"/>
-      <c r="B36" s="15"/>
-      <c r="C36" s="14" t="s">
+      <c r="A36" s="19"/>
+      <c r="B36" s="18"/>
+      <c r="C36" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="D36" s="16"/>
-      <c r="E36" s="16"/>
-      <c r="F36" s="16"/>
-      <c r="G36" s="16"/>
-      <c r="H36" s="15"/>
-      <c r="I36" s="20">
+      <c r="D36" s="20"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="20"/>
+      <c r="G36" s="20"/>
+      <c r="H36" s="18"/>
+      <c r="I36" s="23">
         <f>SUM(J30:J31)</f>
         <v>3000</v>
       </c>
-      <c r="J36" s="15"/>
+      <c r="J36" s="18"/>
     </row>
     <row r="37" spans="1:10" ht="15.75" customHeight="1">
       <c r="A37" s="6"/>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
       <c r="D37" s="6"/>
-      <c r="E37" s="11"/>
+      <c r="E37" s="9"/>
       <c r="F37" s="10"/>
       <c r="G37" s="10"/>
       <c r="H37" s="10"/>
@@ -1280,7 +1280,7 @@
       <c r="J37" s="10"/>
     </row>
     <row r="38" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A38" s="21" t="s">
+      <c r="A38" s="11" t="s">
         <v>13</v>
       </c>
       <c r="B38" s="10"/>
@@ -1290,13 +1290,13 @@
       <c r="F38" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="G38" s="22"/>
-      <c r="H38" s="23"/>
-      <c r="I38" s="23"/>
-      <c r="J38" s="23"/>
+      <c r="G38" s="12"/>
+      <c r="H38" s="13"/>
+      <c r="I38" s="13"/>
+      <c r="J38" s="13"/>
     </row>
     <row r="39" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A39" s="24" t="s">
+      <c r="A39" s="14" t="s">
         <v>15</v>
       </c>
       <c r="B39" s="10"/>
@@ -1304,12 +1304,12 @@
       <c r="D39" s="10"/>
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
-      <c r="G39" s="25" t="s">
+      <c r="G39" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="H39" s="26"/>
-      <c r="I39" s="26"/>
-      <c r="J39" s="26"/>
+      <c r="H39" s="16"/>
+      <c r="I39" s="16"/>
+      <c r="J39" s="16"/>
     </row>
     <row r="40" spans="1:10" ht="15.75" customHeight="1">
       <c r="A40" s="8"/>
@@ -1994,80 +1994,80 @@
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="74">
-    <mergeCell ref="E37:J37"/>
-    <mergeCell ref="A38:D38"/>
-    <mergeCell ref="G38:J38"/>
-    <mergeCell ref="A39:D39"/>
-    <mergeCell ref="G39:J39"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:H8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:H9"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C10:H10"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C13:H13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="C14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:H16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="E17:J17"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="G18:J18"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="G19:J19"/>
+    <mergeCell ref="A22:J22"/>
+    <mergeCell ref="A23:J23"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A26:J26"/>
+    <mergeCell ref="A27:J27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:H28"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C29:H29"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:H30"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:H31"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="C32:H32"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="C33:H33"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="C34:H34"/>
+    <mergeCell ref="I34:J34"/>
     <mergeCell ref="A35:B35"/>
     <mergeCell ref="C35:H35"/>
     <mergeCell ref="I35:J35"/>
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="C36:H36"/>
     <mergeCell ref="I36:J36"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="C33:H33"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="C34:H34"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:H31"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="C32:H32"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C29:H29"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:H30"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="A26:J26"/>
-    <mergeCell ref="A27:J27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:H28"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="G19:J19"/>
-    <mergeCell ref="A22:J22"/>
-    <mergeCell ref="A23:J23"/>
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C16:H16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="E17:J17"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="G18:J18"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="C14:H14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C13:H13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C10:H10"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:H8"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="C9:H9"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="E37:J37"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="G38:J38"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="G39:J39"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0" footer="0"/>

--- a/templates/billing.xlsx
+++ b/templates/billing.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="Billing" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
@@ -256,10 +256,36 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -274,32 +300,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -782,7 +782,7 @@
       <c r="J1" s="2"/>
     </row>
     <row r="2" spans="1:14" ht="38.25" customHeight="1">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="9" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="10"/>
@@ -796,7 +796,7 @@
       <c r="J2" s="10"/>
     </row>
     <row r="3" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="11" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="10"/>
@@ -810,7 +810,7 @@
       <c r="J3" s="10"/>
     </row>
     <row r="4" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="11" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="10"/>
@@ -836,7 +836,7 @@
       <c r="J5" s="4"/>
     </row>
     <row r="6" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A6" s="24" t="s">
+      <c r="A6" s="12" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="10"/>
@@ -850,7 +850,7 @@
       <c r="J6" s="10"/>
     </row>
     <row r="7" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A7" s="25" t="s">
+      <c r="A7" s="13" t="s">
         <v>4</v>
       </c>
       <c r="B7" s="10"/>
@@ -865,143 +865,143 @@
       <c r="N7" s="5"/>
     </row>
     <row r="8" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="18"/>
-      <c r="C8" s="22" t="s">
+      <c r="B8" s="15"/>
+      <c r="C8" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="20"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="20"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="18"/>
-      <c r="I8" s="22" t="s">
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="J8" s="18"/>
+      <c r="J8" s="15"/>
     </row>
     <row r="9" spans="1:14" ht="21" customHeight="1">
       <c r="A9" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="18"/>
-      <c r="C9" s="19" t="s">
+      <c r="B9" s="15"/>
+      <c r="C9" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="18"/>
-      <c r="I9" s="21"/>
-      <c r="J9" s="18"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="15"/>
       <c r="M9" s="6"/>
     </row>
     <row r="10" spans="1:14" ht="14.25" customHeight="1">
       <c r="A10" s="17"/>
-      <c r="B10" s="18"/>
-      <c r="C10" s="19" t="s">
+      <c r="B10" s="15"/>
+      <c r="C10" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="18"/>
-      <c r="I10" s="21">
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="19">
         <v>1500</v>
       </c>
-      <c r="J10" s="18"/>
+      <c r="J10" s="15"/>
     </row>
     <row r="11" spans="1:14" ht="14.25" customHeight="1">
       <c r="A11" s="17"/>
-      <c r="B11" s="18"/>
-      <c r="C11" s="19" t="s">
+      <c r="B11" s="15"/>
+      <c r="C11" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="20"/>
-      <c r="E11" s="20"/>
-      <c r="F11" s="20"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="21">
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="15"/>
+      <c r="I11" s="19">
         <v>1500</v>
       </c>
-      <c r="J11" s="18"/>
+      <c r="J11" s="15"/>
     </row>
     <row r="12" spans="1:14" ht="14.25" customHeight="1">
       <c r="A12" s="17"/>
-      <c r="B12" s="18"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="20"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="18"/>
-      <c r="I12" s="21"/>
-      <c r="J12" s="18"/>
+      <c r="B12" s="15"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="15"/>
     </row>
     <row r="13" spans="1:14" ht="14.25" customHeight="1">
       <c r="A13" s="17"/>
-      <c r="B13" s="18"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="18"/>
-      <c r="I13" s="21"/>
-      <c r="J13" s="18"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="15"/>
     </row>
     <row r="14" spans="1:14" ht="14.25" customHeight="1">
       <c r="A14" s="17"/>
-      <c r="B14" s="18"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="18"/>
-      <c r="I14" s="21"/>
-      <c r="J14" s="18"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="15"/>
     </row>
     <row r="15" spans="1:14" ht="14.25" customHeight="1">
       <c r="A15" s="17"/>
-      <c r="B15" s="18"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="18"/>
-      <c r="I15" s="21"/>
-      <c r="J15" s="18"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="15"/>
     </row>
     <row r="16" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A16" s="19"/>
-      <c r="B16" s="18"/>
-      <c r="C16" s="22" t="s">
+      <c r="A16" s="18"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="18"/>
-      <c r="I16" s="23">
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="20">
         <f>SUM(J10:J11)</f>
         <v>3000</v>
       </c>
-      <c r="J16" s="18"/>
+      <c r="J16" s="15"/>
     </row>
     <row r="17" spans="1:14" ht="14.25" customHeight="1">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
-      <c r="E17" s="9"/>
+      <c r="E17" s="11"/>
       <c r="F17" s="10"/>
       <c r="G17" s="10"/>
       <c r="H17" s="10"/>
@@ -1009,7 +1009,7 @@
       <c r="J17" s="10"/>
     </row>
     <row r="18" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="21" t="s">
         <v>13</v>
       </c>
       <c r="B18" s="10"/>
@@ -1019,13 +1019,13 @@
       <c r="F18" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="G18" s="12"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="13"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="23"/>
+      <c r="I18" s="23"/>
+      <c r="J18" s="23"/>
     </row>
     <row r="19" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="24" t="s">
         <v>15</v>
       </c>
       <c r="B19" s="10"/>
@@ -1033,12 +1033,12 @@
       <c r="D19" s="10"/>
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
-      <c r="G19" s="15" t="s">
+      <c r="G19" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="H19" s="16"/>
-      <c r="I19" s="16"/>
-      <c r="J19" s="16"/>
+      <c r="H19" s="26"/>
+      <c r="I19" s="26"/>
+      <c r="J19" s="26"/>
     </row>
     <row r="20" spans="1:14" ht="76.5" customHeight="1">
       <c r="A20" s="8"/>
@@ -1055,7 +1055,7 @@
     </row>
     <row r="21" spans="1:14" ht="72" customHeight="1"/>
     <row r="22" spans="1:14" ht="78" customHeight="1">
-      <c r="A22" s="26" t="s">
+      <c r="A22" s="9" t="s">
         <v>0</v>
       </c>
       <c r="B22" s="10"/>
@@ -1069,7 +1069,7 @@
       <c r="J22" s="10"/>
     </row>
     <row r="23" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A23" s="9" t="s">
+      <c r="A23" s="11" t="s">
         <v>1</v>
       </c>
       <c r="B23" s="10"/>
@@ -1083,7 +1083,7 @@
       <c r="J23" s="10"/>
     </row>
     <row r="24" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A24" s="9" t="s">
+      <c r="A24" s="11" t="s">
         <v>2</v>
       </c>
       <c r="B24" s="10"/>
@@ -1109,7 +1109,7 @@
       <c r="J25" s="4"/>
     </row>
     <row r="26" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A26" s="24" t="s">
+      <c r="A26" s="12" t="s">
         <v>3</v>
       </c>
       <c r="B26" s="10"/>
@@ -1123,7 +1123,7 @@
       <c r="J26" s="10"/>
     </row>
     <row r="27" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A27" s="25" t="s">
+      <c r="A27" s="13" t="s">
         <v>4</v>
       </c>
       <c r="B27" s="10"/>
@@ -1137,142 +1137,142 @@
       <c r="J27" s="10"/>
     </row>
     <row r="28" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A28" s="22" t="s">
+      <c r="A28" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B28" s="18"/>
-      <c r="C28" s="22" t="s">
+      <c r="B28" s="15"/>
+      <c r="C28" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="18"/>
-      <c r="I28" s="22" t="s">
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="15"/>
+      <c r="I28" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="J28" s="18"/>
+      <c r="J28" s="15"/>
     </row>
     <row r="29" spans="1:14" ht="15.75" customHeight="1">
       <c r="A29" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="B29" s="18"/>
-      <c r="C29" s="19" t="s">
+      <c r="B29" s="15"/>
+      <c r="C29" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="18"/>
-      <c r="I29" s="21"/>
-      <c r="J29" s="18"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="16"/>
+      <c r="H29" s="15"/>
+      <c r="I29" s="19"/>
+      <c r="J29" s="15"/>
     </row>
     <row r="30" spans="1:14" ht="15.75" customHeight="1">
       <c r="A30" s="17"/>
-      <c r="B30" s="18"/>
-      <c r="C30" s="19" t="s">
+      <c r="B30" s="15"/>
+      <c r="C30" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="20"/>
-      <c r="G30" s="20"/>
-      <c r="H30" s="18"/>
-      <c r="I30" s="21">
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="16"/>
+      <c r="H30" s="15"/>
+      <c r="I30" s="19">
         <v>1500</v>
       </c>
-      <c r="J30" s="18"/>
+      <c r="J30" s="15"/>
     </row>
     <row r="31" spans="1:14" ht="15.75" customHeight="1">
       <c r="A31" s="17"/>
-      <c r="B31" s="18"/>
-      <c r="C31" s="19" t="s">
+      <c r="B31" s="15"/>
+      <c r="C31" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="D31" s="20"/>
-      <c r="E31" s="20"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="20"/>
-      <c r="H31" s="18"/>
-      <c r="I31" s="21">
+      <c r="D31" s="16"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="16"/>
+      <c r="H31" s="15"/>
+      <c r="I31" s="19">
         <v>1500</v>
       </c>
-      <c r="J31" s="18"/>
+      <c r="J31" s="15"/>
     </row>
     <row r="32" spans="1:14" ht="15.75" customHeight="1">
       <c r="A32" s="17"/>
-      <c r="B32" s="18"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="20"/>
-      <c r="E32" s="20"/>
-      <c r="F32" s="20"/>
-      <c r="G32" s="20"/>
-      <c r="H32" s="18"/>
-      <c r="I32" s="21"/>
-      <c r="J32" s="18"/>
+      <c r="B32" s="15"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="16"/>
+      <c r="G32" s="16"/>
+      <c r="H32" s="15"/>
+      <c r="I32" s="19"/>
+      <c r="J32" s="15"/>
     </row>
     <row r="33" spans="1:10" ht="15.75" customHeight="1">
       <c r="A33" s="17"/>
-      <c r="B33" s="18"/>
-      <c r="C33" s="19"/>
-      <c r="D33" s="20"/>
-      <c r="E33" s="20"/>
-      <c r="F33" s="20"/>
-      <c r="G33" s="20"/>
-      <c r="H33" s="18"/>
-      <c r="I33" s="21"/>
-      <c r="J33" s="18"/>
+      <c r="B33" s="15"/>
+      <c r="C33" s="18"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="16"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="16"/>
+      <c r="H33" s="15"/>
+      <c r="I33" s="19"/>
+      <c r="J33" s="15"/>
     </row>
     <row r="34" spans="1:10" ht="15.75" customHeight="1">
       <c r="A34" s="17"/>
-      <c r="B34" s="18"/>
-      <c r="C34" s="19"/>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="20"/>
-      <c r="G34" s="20"/>
-      <c r="H34" s="18"/>
-      <c r="I34" s="21"/>
-      <c r="J34" s="18"/>
+      <c r="B34" s="15"/>
+      <c r="C34" s="18"/>
+      <c r="D34" s="16"/>
+      <c r="E34" s="16"/>
+      <c r="F34" s="16"/>
+      <c r="G34" s="16"/>
+      <c r="H34" s="15"/>
+      <c r="I34" s="19"/>
+      <c r="J34" s="15"/>
     </row>
     <row r="35" spans="1:10" ht="15.75" customHeight="1">
       <c r="A35" s="17"/>
-      <c r="B35" s="18"/>
-      <c r="C35" s="19"/>
-      <c r="D35" s="20"/>
-      <c r="E35" s="20"/>
-      <c r="F35" s="20"/>
-      <c r="G35" s="20"/>
-      <c r="H35" s="18"/>
-      <c r="I35" s="21"/>
-      <c r="J35" s="18"/>
+      <c r="B35" s="15"/>
+      <c r="C35" s="18"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="16"/>
+      <c r="H35" s="15"/>
+      <c r="I35" s="19"/>
+      <c r="J35" s="15"/>
     </row>
     <row r="36" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A36" s="19"/>
-      <c r="B36" s="18"/>
-      <c r="C36" s="22" t="s">
+      <c r="A36" s="18"/>
+      <c r="B36" s="15"/>
+      <c r="C36" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="D36" s="20"/>
-      <c r="E36" s="20"/>
-      <c r="F36" s="20"/>
-      <c r="G36" s="20"/>
-      <c r="H36" s="18"/>
-      <c r="I36" s="23">
+      <c r="D36" s="16"/>
+      <c r="E36" s="16"/>
+      <c r="F36" s="16"/>
+      <c r="G36" s="16"/>
+      <c r="H36" s="15"/>
+      <c r="I36" s="20">
         <f>SUM(J30:J31)</f>
         <v>3000</v>
       </c>
-      <c r="J36" s="18"/>
+      <c r="J36" s="15"/>
     </row>
     <row r="37" spans="1:10" ht="15.75" customHeight="1">
       <c r="A37" s="6"/>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
       <c r="D37" s="6"/>
-      <c r="E37" s="9"/>
+      <c r="E37" s="11"/>
       <c r="F37" s="10"/>
       <c r="G37" s="10"/>
       <c r="H37" s="10"/>
@@ -1280,7 +1280,7 @@
       <c r="J37" s="10"/>
     </row>
     <row r="38" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A38" s="11" t="s">
+      <c r="A38" s="21" t="s">
         <v>13</v>
       </c>
       <c r="B38" s="10"/>
@@ -1290,13 +1290,13 @@
       <c r="F38" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="G38" s="12"/>
-      <c r="H38" s="13"/>
-      <c r="I38" s="13"/>
-      <c r="J38" s="13"/>
+      <c r="G38" s="22"/>
+      <c r="H38" s="23"/>
+      <c r="I38" s="23"/>
+      <c r="J38" s="23"/>
     </row>
     <row r="39" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A39" s="14" t="s">
+      <c r="A39" s="24" t="s">
         <v>15</v>
       </c>
       <c r="B39" s="10"/>
@@ -1304,12 +1304,12 @@
       <c r="D39" s="10"/>
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
-      <c r="G39" s="15" t="s">
+      <c r="G39" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="H39" s="16"/>
-      <c r="I39" s="16"/>
-      <c r="J39" s="16"/>
+      <c r="H39" s="26"/>
+      <c r="I39" s="26"/>
+      <c r="J39" s="26"/>
     </row>
     <row r="40" spans="1:10" ht="15.75" customHeight="1">
       <c r="A40" s="8"/>
@@ -1992,86 +1992,85 @@
     <row r="707" ht="15.75" customHeight="1"/>
     <row r="708" ht="15.75" customHeight="1"/>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="74">
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="E37:J37"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="G38:J38"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="G39:J39"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="C35:H35"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="C36:H36"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="C33:H33"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="C34:H34"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:H31"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="C32:H32"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C29:H29"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:H30"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="A26:J26"/>
+    <mergeCell ref="A27:J27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:H28"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="G19:J19"/>
+    <mergeCell ref="A22:J22"/>
+    <mergeCell ref="A23:J23"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:H16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="E17:J17"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="G18:J18"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="C14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C13:H13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C10:H10"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C11:H11"/>
+    <mergeCell ref="I11:J11"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="C8:H8"/>
     <mergeCell ref="I8:J8"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="C9:H9"/>
     <mergeCell ref="I9:J9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C10:H10"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C13:H13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="C14:H14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C16:H16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="E17:J17"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="G18:J18"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="G19:J19"/>
-    <mergeCell ref="A22:J22"/>
-    <mergeCell ref="A23:J23"/>
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="A26:J26"/>
-    <mergeCell ref="A27:J27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:H28"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C29:H29"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:H30"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:H31"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="C32:H32"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="C33:H33"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="C34:H34"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="C35:H35"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="C36:H36"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="E37:J37"/>
-    <mergeCell ref="A38:D38"/>
-    <mergeCell ref="G38:J38"/>
-    <mergeCell ref="A39:D39"/>
-    <mergeCell ref="G39:J39"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A7:J7"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="1" right="1" top="1" bottom="1" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="77" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="1.25" right="1" top="1" bottom="1" header="0" footer="0"/>
+  <pageSetup paperSize="9" scale="66" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/templates/billing.xlsx
+++ b/templates/billing.xlsx
@@ -256,36 +256,10 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -300,6 +274,32 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -321,10 +321,10 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>695325</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1381125" cy="923925"/>
     <xdr:pic>
@@ -348,8 +348,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
+          <a:off x="1276350" y="1038225"/>
+          <a:ext cx="1381125" cy="923925"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -360,10 +360,10 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>695325</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1381125" cy="923925"/>
     <xdr:pic>
@@ -387,8 +387,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
+          <a:off x="1276350" y="7067550"/>
+          <a:ext cx="1381125" cy="923925"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -782,7 +782,7 @@
       <c r="J1" s="2"/>
     </row>
     <row r="2" spans="1:14" ht="38.25" customHeight="1">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="26" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="10"/>
@@ -796,7 +796,7 @@
       <c r="J2" s="10"/>
     </row>
     <row r="3" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="9" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="10"/>
@@ -810,7 +810,7 @@
       <c r="J3" s="10"/>
     </row>
     <row r="4" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="9" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="10"/>
@@ -836,7 +836,7 @@
       <c r="J5" s="4"/>
     </row>
     <row r="6" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="24" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="10"/>
@@ -850,7 +850,7 @@
       <c r="J6" s="10"/>
     </row>
     <row r="7" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="25" t="s">
         <v>4</v>
       </c>
       <c r="B7" s="10"/>
@@ -865,143 +865,143 @@
       <c r="N7" s="5"/>
     </row>
     <row r="8" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="15"/>
-      <c r="C8" s="14" t="s">
+      <c r="B8" s="18"/>
+      <c r="C8" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="14" t="s">
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="J8" s="15"/>
+      <c r="J8" s="18"/>
     </row>
     <row r="9" spans="1:14" ht="21" customHeight="1">
       <c r="A9" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="15"/>
-      <c r="C9" s="18" t="s">
+      <c r="B9" s="18"/>
+      <c r="C9" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="19"/>
-      <c r="J9" s="15"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="21"/>
+      <c r="J9" s="18"/>
       <c r="M9" s="6"/>
     </row>
     <row r="10" spans="1:14" ht="14.25" customHeight="1">
       <c r="A10" s="17"/>
-      <c r="B10" s="15"/>
-      <c r="C10" s="18" t="s">
+      <c r="B10" s="18"/>
+      <c r="C10" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="19">
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="21">
         <v>1500</v>
       </c>
-      <c r="J10" s="15"/>
+      <c r="J10" s="18"/>
     </row>
     <row r="11" spans="1:14" ht="14.25" customHeight="1">
       <c r="A11" s="17"/>
-      <c r="B11" s="15"/>
-      <c r="C11" s="18" t="s">
+      <c r="B11" s="18"/>
+      <c r="C11" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="19">
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="21">
         <v>1500</v>
       </c>
-      <c r="J11" s="15"/>
+      <c r="J11" s="18"/>
     </row>
     <row r="12" spans="1:14" ht="14.25" customHeight="1">
       <c r="A12" s="17"/>
-      <c r="B12" s="15"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="15"/>
-      <c r="I12" s="19"/>
-      <c r="J12" s="15"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="18"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="18"/>
     </row>
     <row r="13" spans="1:14" ht="14.25" customHeight="1">
       <c r="A13" s="17"/>
-      <c r="B13" s="15"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="15"/>
-      <c r="I13" s="19"/>
-      <c r="J13" s="15"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="21"/>
+      <c r="J13" s="18"/>
     </row>
     <row r="14" spans="1:14" ht="14.25" customHeight="1">
       <c r="A14" s="17"/>
-      <c r="B14" s="15"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="15"/>
-      <c r="I14" s="19"/>
-      <c r="J14" s="15"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="18"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="18"/>
     </row>
     <row r="15" spans="1:14" ht="14.25" customHeight="1">
       <c r="A15" s="17"/>
-      <c r="B15" s="15"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="19"/>
-      <c r="J15" s="15"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="21"/>
+      <c r="J15" s="18"/>
     </row>
     <row r="16" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A16" s="18"/>
-      <c r="B16" s="15"/>
-      <c r="C16" s="14" t="s">
+      <c r="A16" s="19"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="20">
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="18"/>
+      <c r="I16" s="23">
         <f>SUM(J10:J11)</f>
         <v>3000</v>
       </c>
-      <c r="J16" s="15"/>
+      <c r="J16" s="18"/>
     </row>
     <row r="17" spans="1:14" ht="14.25" customHeight="1">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
-      <c r="E17" s="11"/>
+      <c r="E17" s="9"/>
       <c r="F17" s="10"/>
       <c r="G17" s="10"/>
       <c r="H17" s="10"/>
@@ -1009,7 +1009,7 @@
       <c r="J17" s="10"/>
     </row>
     <row r="18" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A18" s="21" t="s">
+      <c r="A18" s="11" t="s">
         <v>13</v>
       </c>
       <c r="B18" s="10"/>
@@ -1019,13 +1019,13 @@
       <c r="F18" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="G18" s="22"/>
-      <c r="H18" s="23"/>
-      <c r="I18" s="23"/>
-      <c r="J18" s="23"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="13"/>
+      <c r="J18" s="13"/>
     </row>
     <row r="19" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A19" s="24" t="s">
+      <c r="A19" s="14" t="s">
         <v>15</v>
       </c>
       <c r="B19" s="10"/>
@@ -1033,12 +1033,12 @@
       <c r="D19" s="10"/>
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
-      <c r="G19" s="25" t="s">
+      <c r="G19" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="H19" s="26"/>
-      <c r="I19" s="26"/>
-      <c r="J19" s="26"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="16"/>
+      <c r="J19" s="16"/>
     </row>
     <row r="20" spans="1:14" ht="76.5" customHeight="1">
       <c r="A20" s="8"/>
@@ -1055,7 +1055,7 @@
     </row>
     <row r="21" spans="1:14" ht="72" customHeight="1"/>
     <row r="22" spans="1:14" ht="78" customHeight="1">
-      <c r="A22" s="9" t="s">
+      <c r="A22" s="26" t="s">
         <v>0</v>
       </c>
       <c r="B22" s="10"/>
@@ -1069,7 +1069,7 @@
       <c r="J22" s="10"/>
     </row>
     <row r="23" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A23" s="11" t="s">
+      <c r="A23" s="9" t="s">
         <v>1</v>
       </c>
       <c r="B23" s="10"/>
@@ -1083,7 +1083,7 @@
       <c r="J23" s="10"/>
     </row>
     <row r="24" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A24" s="11" t="s">
+      <c r="A24" s="9" t="s">
         <v>2</v>
       </c>
       <c r="B24" s="10"/>
@@ -1109,7 +1109,7 @@
       <c r="J25" s="4"/>
     </row>
     <row r="26" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A26" s="12" t="s">
+      <c r="A26" s="24" t="s">
         <v>3</v>
       </c>
       <c r="B26" s="10"/>
@@ -1123,7 +1123,7 @@
       <c r="J26" s="10"/>
     </row>
     <row r="27" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A27" s="13" t="s">
+      <c r="A27" s="25" t="s">
         <v>4</v>
       </c>
       <c r="B27" s="10"/>
@@ -1137,142 +1137,142 @@
       <c r="J27" s="10"/>
     </row>
     <row r="28" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A28" s="14" t="s">
+      <c r="A28" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="B28" s="15"/>
-      <c r="C28" s="14" t="s">
+      <c r="B28" s="18"/>
+      <c r="C28" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="16"/>
-      <c r="H28" s="15"/>
-      <c r="I28" s="14" t="s">
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
+      <c r="H28" s="18"/>
+      <c r="I28" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="J28" s="15"/>
+      <c r="J28" s="18"/>
     </row>
     <row r="29" spans="1:14" ht="15.75" customHeight="1">
       <c r="A29" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="B29" s="15"/>
-      <c r="C29" s="18" t="s">
+      <c r="B29" s="18"/>
+      <c r="C29" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="16"/>
-      <c r="G29" s="16"/>
-      <c r="H29" s="15"/>
-      <c r="I29" s="19"/>
-      <c r="J29" s="15"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="18"/>
+      <c r="I29" s="21"/>
+      <c r="J29" s="18"/>
     </row>
     <row r="30" spans="1:14" ht="15.75" customHeight="1">
       <c r="A30" s="17"/>
-      <c r="B30" s="15"/>
-      <c r="C30" s="18" t="s">
+      <c r="B30" s="18"/>
+      <c r="C30" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="16"/>
-      <c r="G30" s="16"/>
-      <c r="H30" s="15"/>
-      <c r="I30" s="19">
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
+      <c r="H30" s="18"/>
+      <c r="I30" s="21">
         <v>1500</v>
       </c>
-      <c r="J30" s="15"/>
+      <c r="J30" s="18"/>
     </row>
     <row r="31" spans="1:14" ht="15.75" customHeight="1">
       <c r="A31" s="17"/>
-      <c r="B31" s="15"/>
-      <c r="C31" s="18" t="s">
+      <c r="B31" s="18"/>
+      <c r="C31" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="D31" s="16"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="16"/>
-      <c r="H31" s="15"/>
-      <c r="I31" s="19">
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="20"/>
+      <c r="H31" s="18"/>
+      <c r="I31" s="21">
         <v>1500</v>
       </c>
-      <c r="J31" s="15"/>
+      <c r="J31" s="18"/>
     </row>
     <row r="32" spans="1:14" ht="15.75" customHeight="1">
       <c r="A32" s="17"/>
-      <c r="B32" s="15"/>
-      <c r="C32" s="18"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16"/>
-      <c r="F32" s="16"/>
-      <c r="G32" s="16"/>
-      <c r="H32" s="15"/>
-      <c r="I32" s="19"/>
-      <c r="J32" s="15"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="20"/>
+      <c r="H32" s="18"/>
+      <c r="I32" s="21"/>
+      <c r="J32" s="18"/>
     </row>
     <row r="33" spans="1:10" ht="15.75" customHeight="1">
       <c r="A33" s="17"/>
-      <c r="B33" s="15"/>
-      <c r="C33" s="18"/>
-      <c r="D33" s="16"/>
-      <c r="E33" s="16"/>
-      <c r="F33" s="16"/>
-      <c r="G33" s="16"/>
-      <c r="H33" s="15"/>
-      <c r="I33" s="19"/>
-      <c r="J33" s="15"/>
+      <c r="B33" s="18"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="20"/>
+      <c r="H33" s="18"/>
+      <c r="I33" s="21"/>
+      <c r="J33" s="18"/>
     </row>
     <row r="34" spans="1:10" ht="15.75" customHeight="1">
       <c r="A34" s="17"/>
-      <c r="B34" s="15"/>
-      <c r="C34" s="18"/>
-      <c r="D34" s="16"/>
-      <c r="E34" s="16"/>
-      <c r="F34" s="16"/>
-      <c r="G34" s="16"/>
-      <c r="H34" s="15"/>
-      <c r="I34" s="19"/>
-      <c r="J34" s="15"/>
+      <c r="B34" s="18"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="20"/>
+      <c r="H34" s="18"/>
+      <c r="I34" s="21"/>
+      <c r="J34" s="18"/>
     </row>
     <row r="35" spans="1:10" ht="15.75" customHeight="1">
       <c r="A35" s="17"/>
-      <c r="B35" s="15"/>
-      <c r="C35" s="18"/>
-      <c r="D35" s="16"/>
-      <c r="E35" s="16"/>
-      <c r="F35" s="16"/>
-      <c r="G35" s="16"/>
-      <c r="H35" s="15"/>
-      <c r="I35" s="19"/>
-      <c r="J35" s="15"/>
+      <c r="B35" s="18"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="20"/>
+      <c r="G35" s="20"/>
+      <c r="H35" s="18"/>
+      <c r="I35" s="21"/>
+      <c r="J35" s="18"/>
     </row>
     <row r="36" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A36" s="18"/>
-      <c r="B36" s="15"/>
-      <c r="C36" s="14" t="s">
+      <c r="A36" s="19"/>
+      <c r="B36" s="18"/>
+      <c r="C36" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="D36" s="16"/>
-      <c r="E36" s="16"/>
-      <c r="F36" s="16"/>
-      <c r="G36" s="16"/>
-      <c r="H36" s="15"/>
-      <c r="I36" s="20">
+      <c r="D36" s="20"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="20"/>
+      <c r="G36" s="20"/>
+      <c r="H36" s="18"/>
+      <c r="I36" s="23">
         <f>SUM(J30:J31)</f>
         <v>3000</v>
       </c>
-      <c r="J36" s="15"/>
+      <c r="J36" s="18"/>
     </row>
     <row r="37" spans="1:10" ht="15.75" customHeight="1">
       <c r="A37" s="6"/>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
       <c r="D37" s="6"/>
-      <c r="E37" s="11"/>
+      <c r="E37" s="9"/>
       <c r="F37" s="10"/>
       <c r="G37" s="10"/>
       <c r="H37" s="10"/>
@@ -1280,7 +1280,7 @@
       <c r="J37" s="10"/>
     </row>
     <row r="38" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A38" s="21" t="s">
+      <c r="A38" s="11" t="s">
         <v>13</v>
       </c>
       <c r="B38" s="10"/>
@@ -1290,13 +1290,13 @@
       <c r="F38" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="G38" s="22"/>
-      <c r="H38" s="23"/>
-      <c r="I38" s="23"/>
-      <c r="J38" s="23"/>
+      <c r="G38" s="12"/>
+      <c r="H38" s="13"/>
+      <c r="I38" s="13"/>
+      <c r="J38" s="13"/>
     </row>
     <row r="39" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A39" s="24" t="s">
+      <c r="A39" s="14" t="s">
         <v>15</v>
       </c>
       <c r="B39" s="10"/>
@@ -1304,12 +1304,12 @@
       <c r="D39" s="10"/>
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
-      <c r="G39" s="25" t="s">
+      <c r="G39" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="H39" s="26"/>
-      <c r="I39" s="26"/>
-      <c r="J39" s="26"/>
+      <c r="H39" s="16"/>
+      <c r="I39" s="16"/>
+      <c r="J39" s="16"/>
     </row>
     <row r="40" spans="1:10" ht="15.75" customHeight="1">
       <c r="A40" s="8"/>
@@ -1993,80 +1993,80 @@
     <row r="708" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="74">
-    <mergeCell ref="E37:J37"/>
-    <mergeCell ref="A38:D38"/>
-    <mergeCell ref="G38:J38"/>
-    <mergeCell ref="A39:D39"/>
-    <mergeCell ref="G39:J39"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:H8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:H9"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C10:H10"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C13:H13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="C14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:H16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="E17:J17"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="G18:J18"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="G19:J19"/>
+    <mergeCell ref="A22:J22"/>
+    <mergeCell ref="A23:J23"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A26:J26"/>
+    <mergeCell ref="A27:J27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:H28"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C29:H29"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:H30"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:H31"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="C32:H32"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="C33:H33"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="C34:H34"/>
+    <mergeCell ref="I34:J34"/>
     <mergeCell ref="A35:B35"/>
     <mergeCell ref="C35:H35"/>
     <mergeCell ref="I35:J35"/>
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="C36:H36"/>
     <mergeCell ref="I36:J36"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="C33:H33"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="C34:H34"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:H31"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="C32:H32"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C29:H29"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:H30"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="A26:J26"/>
-    <mergeCell ref="A27:J27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:H28"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="G19:J19"/>
-    <mergeCell ref="A22:J22"/>
-    <mergeCell ref="A23:J23"/>
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C16:H16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="E17:J17"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="G18:J18"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="C14:H14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C13:H13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C10:H10"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:H8"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="C9:H9"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="E37:J37"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="G38:J38"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="G39:J39"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="1.25" right="1" top="1" bottom="1" header="0" footer="0"/>
